--- a/tests/fixtures/manual_spill_cache/cut_whole.xlsx
+++ b/tests/fixtures/manual_spill_cache/cut_whole.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\pyOpenVBA\tests\fixtures\manual_spill_cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45FB5CCC-442B-4884-9EDC-5FEB359615C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FB132CA-4DBC-4897-B04C-0B8EA32F0239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="7200" windowHeight="4545" xr2:uid="{0BBEA796-4662-4CC2-BB20-72F0616CDAEA}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="7200" windowHeight="4545" xr2:uid="{6F16CADF-B71B-4E8C-8641-FE1CFF897775}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -427,7 +427,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FC1F950-5C5E-41CB-818D-12950BA544C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F3A98B-7886-4994-A82F-262BA7C353BA}">
   <dimension ref="E2:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -462,7 +462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08AEEB96-71EB-45DF-BB34-EB477FD0A90B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44E1BCD4-DB4B-480E-8B6E-4E0A7F276BBD}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
